--- a/output/laminas_comunales/comunal_o_ocup_a_2024_atacama.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2024_atacama.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>43.6499034087368</v>
+        <v>62.1148003472222</v>
       </c>
     </row>
     <row r="3">
@@ -399,52 +399,52 @@
         </is>
       </c>
       <c r="C3">
-        <v>41.4583926171158</v>
+        <v>60.0264229502196</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chañaral</t>
+          <t>Diego de Almagro</t>
         </is>
       </c>
       <c r="C4">
-        <v>36.3143349165347</v>
+        <v>58.927424534361</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vallenar</t>
+          <t>Chañaral</t>
         </is>
       </c>
       <c r="C5">
-        <v>35.6537294460163</v>
+        <v>58.8160364709037</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tierra Amarilla</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="C6">
-        <v>35.4125350206189</v>
+        <v>58.3639505507893</v>
       </c>
     </row>
     <row r="7">
@@ -459,52 +459,1177 @@
         </is>
       </c>
       <c r="C7">
-        <v>35.2044844465498</v>
+        <v>56.2809869710596</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Freirina</t>
+          <t>Vallenar</t>
         </is>
       </c>
       <c r="C8">
-        <v>32.608226664749</v>
+        <v>56.0774987316083</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Caldera</t>
+          <t>Chañaral</t>
         </is>
       </c>
       <c r="C9">
-        <v>31.4201455846841</v>
+        <v>55.5917912822144</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>55.3681791770113</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>54.5406742963192</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>54.5355656451003</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>53.9162112932605</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>52.6800648574842</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>52.5557368134856</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>50.3003839960362</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>50.1587301587302</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>49.262592175978</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>49.0995874157221</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>3302</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Alto del Carmen</t>
         </is>
       </c>
-      <c r="C10">
+      <c r="C20">
+        <v>48.97109644989</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>48.7031986818931</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>48.2767584097859</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>47.4825584461572</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>47.3271122685185</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>46.9079251143853</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>45.6335973322218</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>45.1184154306293</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>44.119688234038</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>44.0223744103855</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>43.6499034087368</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>43.1120288013554</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>42.694143000077</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>42.4871089880671</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>41.95463093559</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>41.4583926171158</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>39.9823322232256</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>39.7715758403454</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>39.7235905856596</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>37.9302536231884</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>37.1457656060158</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>36.3143349165347</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>35.6537294460163</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>35.4125350206189</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>35.2044844465498</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>34.7887068937139</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>33.6383127127015</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>32.8277009728623</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>32.6201201201201</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>32.608226664749</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>32.2084392436151</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>31.6608651510207</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>31.4201455846841</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>30.5363179157391</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>30.2135582915337</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>29.2308121374386</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>28.9772098683483</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>28.9320250284414</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>28.8842055965344</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>28.6535887569015</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>27.9598840305307</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C61">
         <v>27.9571646010002</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>27.8487059232239</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>27.8313084764698</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>27.3860471435364</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>27.3636425694587</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>26.8401961346562</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>26.0397074190178</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>25.0763780551222</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>24.9880109192858</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>24.7271900575932</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>22.8583765112263</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>22.6781023025807</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>22.5899992927364</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>18.8940092165899</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>14.9899333081666</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>13.7791741472172</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>13.6564934084191</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>13.2267978684113</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>12.2815430520034</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>11.3181972212809</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>10.6835399449036</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>10.5022651344213</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>10.493705743509</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>10.1917712691771</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>8.68721461187215</v>
       </c>
     </row>
   </sheetData>
